--- a/dados.xlsx
+++ b/dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\diasr\OneDrive\Área de Trabalho\Docs Para Salvar\NOMYNAL\REPORT FINANCEIRO\CLAUDE\Dashboard Financeiro Gerencial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DABB24C5-C208-46CA-B349-FB96E4A88FE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D3DBDEA-2478-40D5-B3AA-00677D6D73C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{F0C8FD1A-3145-4E83-BD6B-DC10C4D6167D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{F0C8FD1A-3145-4E83-BD6B-DC10C4D6167D}"/>
   </bookViews>
   <sheets>
     <sheet name="Faturamento" sheetId="2" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3169" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3171" uniqueCount="160">
   <si>
     <t>Período</t>
   </si>
@@ -543,6 +543,9 @@
   <si>
     <t>13/07/2026</t>
   </si>
+  <si>
+    <t>29/07/2026</t>
+  </si>
 </sst>
 </file>
 
@@ -885,10 +888,10 @@
     <xf numFmtId="43" fontId="6" fillId="4" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="4" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="17" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1151,8 +1154,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB5026CB-91A8-4E60-BB15-DB9F6E7122A5}" name="Tabela1" displayName="Tabela1" ref="A1:C13" totalsRowShown="0">
-  <autoFilter ref="A1:C13" xr:uid="{BB5026CB-91A8-4E60-BB15-DB9F6E7122A5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BB5026CB-91A8-4E60-BB15-DB9F6E7122A5}" name="Tabela1" displayName="Tabela1" ref="A1:C14" totalsRowShown="0">
+  <autoFilter ref="A1:C14" xr:uid="{BB5026CB-91A8-4E60-BB15-DB9F6E7122A5}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{960ED2DE-9545-4CC8-9B5F-0D2F4AE9105B}" name="Nome do cliente"/>
     <tableColumn id="2" xr3:uid="{498A7C36-571A-4FF0-9BDC-3288479EC596}" name="Competência"/>
@@ -17211,102 +17214,102 @@
       <c r="A1" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="43">
+      <c r="B1" s="44">
         <v>45689</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43">
+      <c r="C1" s="44"/>
+      <c r="D1" s="44">
         <v>45717</v>
       </c>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43">
+      <c r="E1" s="44"/>
+      <c r="F1" s="44">
         <v>45748</v>
       </c>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43">
+      <c r="G1" s="44"/>
+      <c r="H1" s="44">
         <v>45778</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43">
+      <c r="I1" s="44"/>
+      <c r="J1" s="44">
         <v>45809</v>
       </c>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43">
+      <c r="K1" s="44"/>
+      <c r="L1" s="44">
         <v>45839</v>
       </c>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43">
+      <c r="M1" s="44"/>
+      <c r="N1" s="44">
         <v>45870</v>
       </c>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43">
+      <c r="O1" s="44"/>
+      <c r="P1" s="44">
         <v>45901</v>
       </c>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43">
+      <c r="Q1" s="44"/>
+      <c r="R1" s="44">
         <v>45931</v>
       </c>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43">
+      <c r="S1" s="44"/>
+      <c r="T1" s="44">
         <v>45962</v>
       </c>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43">
+      <c r="U1" s="44"/>
+      <c r="V1" s="44">
         <v>45992</v>
       </c>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43">
+      <c r="W1" s="44"/>
+      <c r="X1" s="44">
         <v>46023</v>
       </c>
-      <c r="Y1" s="43"/>
-      <c r="Z1" s="43">
+      <c r="Y1" s="44"/>
+      <c r="Z1" s="44">
         <v>46054</v>
       </c>
-      <c r="AA1" s="43"/>
-      <c r="AB1" s="43">
+      <c r="AA1" s="44"/>
+      <c r="AB1" s="44">
         <v>46082</v>
       </c>
-      <c r="AC1" s="43"/>
-      <c r="AD1" s="43">
+      <c r="AC1" s="44"/>
+      <c r="AD1" s="44">
         <v>46113</v>
       </c>
-      <c r="AE1" s="43"/>
-      <c r="AF1" s="43">
+      <c r="AE1" s="44"/>
+      <c r="AF1" s="44">
         <v>46143</v>
       </c>
-      <c r="AG1" s="43"/>
-      <c r="AH1" s="43">
+      <c r="AG1" s="44"/>
+      <c r="AH1" s="44">
         <v>46174</v>
       </c>
-      <c r="AI1" s="43"/>
-      <c r="AJ1" s="43">
+      <c r="AI1" s="44"/>
+      <c r="AJ1" s="44">
         <v>46204</v>
       </c>
-      <c r="AK1" s="43"/>
-      <c r="AL1" s="43">
+      <c r="AK1" s="44"/>
+      <c r="AL1" s="44">
         <v>46235</v>
       </c>
-      <c r="AM1" s="43"/>
-      <c r="AN1" s="43">
+      <c r="AM1" s="44"/>
+      <c r="AN1" s="44">
         <v>46266</v>
       </c>
-      <c r="AO1" s="43"/>
-      <c r="AP1" s="43">
+      <c r="AO1" s="44"/>
+      <c r="AP1" s="44">
         <v>46296</v>
       </c>
-      <c r="AQ1" s="43"/>
-      <c r="AR1" s="43">
+      <c r="AQ1" s="44"/>
+      <c r="AR1" s="44">
         <v>46327</v>
       </c>
-      <c r="AS1" s="43"/>
-      <c r="AT1" s="43">
+      <c r="AS1" s="44"/>
+      <c r="AT1" s="44">
         <v>46357</v>
       </c>
-      <c r="AU1" s="43"/>
-      <c r="AV1" s="44" t="s">
+      <c r="AU1" s="44"/>
+      <c r="AV1" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="AW1" s="44"/>
+      <c r="AW1" s="43"/>
     </row>
     <row r="2" spans="1:49" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="21" t="s">
@@ -17570,34 +17573,34 @@
         <v>375744.29</v>
       </c>
       <c r="AL3" s="5">
-        <v>646519.23</v>
+        <v>617510.72</v>
       </c>
       <c r="AM3" s="5">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AN3" s="5">
-        <v>672566.23</v>
+        <v>661775.76</v>
       </c>
       <c r="AO3" s="5">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AP3" s="5">
-        <v>660892.56999999995</v>
+        <v>653266.75</v>
       </c>
       <c r="AQ3" s="5">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AR3" s="5">
-        <v>642288.49</v>
+        <v>636963.31000000006</v>
       </c>
       <c r="AS3" s="5">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AT3" s="5">
-        <v>620415.09</v>
+        <v>617679.37</v>
       </c>
       <c r="AU3" s="5">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AV3" s="5">
         <v>0</v>
@@ -17713,48 +17716,48 @@
         <v>194212.19</v>
       </c>
       <c r="AJ4" s="6">
-        <v>166667.64000000001</v>
+        <v>182595.31</v>
       </c>
       <c r="AK4" s="6">
-        <v>46922.2</v>
+        <v>158091.01</v>
       </c>
       <c r="AL4" s="6">
-        <v>54096.02</v>
+        <v>75516.02</v>
       </c>
       <c r="AM4" s="6">
         <v>0</v>
       </c>
       <c r="AN4" s="6">
-        <v>15202.38</v>
+        <v>18883.740000000002</v>
       </c>
       <c r="AO4" s="6">
         <v>0</v>
       </c>
       <c r="AP4" s="6">
-        <v>8266.89</v>
+        <v>10856.35</v>
       </c>
       <c r="AQ4" s="6">
         <v>0</v>
       </c>
       <c r="AR4" s="6">
-        <v>4668.66</v>
+        <v>7258.12</v>
       </c>
       <c r="AS4" s="6">
         <v>0</v>
       </c>
       <c r="AT4" s="6">
-        <v>1675.44</v>
+        <v>3584.9</v>
       </c>
       <c r="AU4" s="6">
         <v>0</v>
       </c>
       <c r="AV4" s="6">
         <f>SUM(B4+D4+F4+H4+J4+L4+N4+P4+R4+T4+V4+X4+Z4+AB4+AD4+AF4+AH4+AJ4+AL4+AN4+AP4+AR4+AT4)</f>
-        <v>1845141.4499999997</v>
+        <v>1893258.86</v>
       </c>
       <c r="AW4" s="26">
         <f>SUM(C4+E4+G4+I4+K4+M4+O4+Q4+S4+U4+W4+Y4+AA4+AC4+AE4+AG4+AI4+AK4+AM4+AO4+AQ4+AS4+AU4)</f>
-        <v>1489328.4500000002</v>
+        <v>1600497.2600000002</v>
       </c>
     </row>
     <row r="5" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17864,48 +17867,48 @@
         <v>191427.26</v>
       </c>
       <c r="AJ5" s="7">
-        <v>162401.85</v>
+        <v>177519.16</v>
       </c>
       <c r="AK5" s="7">
-        <v>42656.41</v>
+        <v>153014.85999999999</v>
       </c>
       <c r="AL5" s="7">
-        <v>54096.02</v>
+        <v>75516.02</v>
       </c>
       <c r="AM5" s="7">
         <v>0</v>
       </c>
       <c r="AN5" s="7">
-        <v>15202.38</v>
+        <v>18883.740000000002</v>
       </c>
       <c r="AO5" s="7">
         <v>0</v>
       </c>
       <c r="AP5" s="7">
-        <v>8266.89</v>
+        <v>10856.35</v>
       </c>
       <c r="AQ5" s="7">
         <v>0</v>
       </c>
       <c r="AR5" s="7">
-        <v>4668.66</v>
+        <v>7258.12</v>
       </c>
       <c r="AS5" s="7">
         <v>0</v>
       </c>
       <c r="AT5" s="7">
-        <v>1675.44</v>
+        <v>3584.9</v>
       </c>
       <c r="AU5" s="7">
         <v>0</v>
       </c>
       <c r="AV5" s="7">
         <f t="shared" ref="AV5:AV68" si="0">SUM(B5+D5+F5+H5+J5+L5+N5+P5+R5+T5+V5+X5+Z5+AB5+AD5+AF5+AH5+AJ5+AL5+AN5+AP5+AR5+AT5)</f>
-        <v>1677465.77</v>
+        <v>1724772.8200000003</v>
       </c>
       <c r="AW5" s="28">
         <f t="shared" ref="AW5:AW68" si="1">SUM(C5+E5+G5+I5+K5+M5+O5+Q5+S5+U5+W5+Y5+AA5+AC5+AE5+AG5+AI5+AK5+AM5+AO5+AQ5+AS5+AU5)</f>
-        <v>1321652.77</v>
+        <v>1432011.2200000002</v>
       </c>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.25">
@@ -18166,48 +18169,48 @@
         <v>191427.26</v>
       </c>
       <c r="AJ7" s="8">
-        <v>162401.85</v>
+        <v>177519.16</v>
       </c>
       <c r="AK7" s="9">
-        <v>42656.41</v>
+        <v>153014.85999999999</v>
       </c>
       <c r="AL7" s="8">
-        <v>54096.02</v>
+        <v>75516.02</v>
       </c>
       <c r="AM7" s="9">
         <v>0</v>
       </c>
       <c r="AN7" s="8">
-        <v>15202.38</v>
+        <v>18883.740000000002</v>
       </c>
       <c r="AO7" s="9">
         <v>0</v>
       </c>
       <c r="AP7" s="8">
-        <v>8266.89</v>
+        <v>10856.35</v>
       </c>
       <c r="AQ7" s="9">
         <v>0</v>
       </c>
       <c r="AR7" s="8">
-        <v>4668.66</v>
+        <v>7258.12</v>
       </c>
       <c r="AS7" s="9">
         <v>0</v>
       </c>
       <c r="AT7" s="8">
-        <v>1675.44</v>
+        <v>3584.9</v>
       </c>
       <c r="AU7" s="9">
         <v>0</v>
       </c>
       <c r="AV7" s="8">
         <f t="shared" si="0"/>
-        <v>1672465.77</v>
+        <v>1719772.8200000003</v>
       </c>
       <c r="AW7" s="30">
         <f t="shared" si="1"/>
-        <v>1316652.77</v>
+        <v>1427011.2200000002</v>
       </c>
     </row>
     <row r="8" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18317,10 +18320,10 @@
         <v>586.03</v>
       </c>
       <c r="AJ8" s="7">
-        <v>3481.12</v>
+        <v>4522.59</v>
       </c>
       <c r="AK8" s="7">
-        <v>3481.12</v>
+        <v>4522.59</v>
       </c>
       <c r="AL8" s="7">
         <v>0</v>
@@ -18354,11 +18357,11 @@
       </c>
       <c r="AV8" s="7">
         <f t="shared" si="0"/>
-        <v>13857.05</v>
+        <v>14898.52</v>
       </c>
       <c r="AW8" s="28">
         <f t="shared" si="1"/>
-        <v>13857.05</v>
+        <v>14898.52</v>
       </c>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.25">
@@ -18468,10 +18471,10 @@
         <v>586.03</v>
       </c>
       <c r="AJ9" s="8">
-        <v>3481.12</v>
+        <v>4522.59</v>
       </c>
       <c r="AK9" s="9">
-        <v>3481.12</v>
+        <v>4522.59</v>
       </c>
       <c r="AL9" s="8">
         <v>0</v>
@@ -18505,11 +18508,11 @@
       </c>
       <c r="AV9" s="8">
         <f t="shared" si="0"/>
-        <v>13857.05</v>
+        <v>14898.52</v>
       </c>
       <c r="AW9" s="30">
         <f t="shared" si="1"/>
-        <v>13857.05</v>
+        <v>14898.52</v>
       </c>
     </row>
     <row r="10" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18619,10 +18622,10 @@
         <v>2198.9</v>
       </c>
       <c r="AJ10" s="7">
-        <v>534.66999999999996</v>
+        <v>553.55999999999995</v>
       </c>
       <c r="AK10" s="7">
-        <v>534.66999999999996</v>
+        <v>553.55999999999995</v>
       </c>
       <c r="AL10" s="7">
         <v>0</v>
@@ -18656,11 +18659,11 @@
       </c>
       <c r="AV10" s="7">
         <f t="shared" si="0"/>
-        <v>51571.53</v>
+        <v>51590.42</v>
       </c>
       <c r="AW10" s="28">
         <f t="shared" si="1"/>
-        <v>51571.53</v>
+        <v>51590.42</v>
       </c>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.25">
@@ -18770,10 +18773,10 @@
         <v>1201.0899999999999</v>
       </c>
       <c r="AJ11" s="8">
-        <v>534.66999999999996</v>
+        <v>553.55999999999995</v>
       </c>
       <c r="AK11" s="9">
-        <v>534.66999999999996</v>
+        <v>553.55999999999995</v>
       </c>
       <c r="AL11" s="8">
         <v>0</v>
@@ -18807,11 +18810,11 @@
       </c>
       <c r="AV11" s="8">
         <f t="shared" si="0"/>
-        <v>3921.1900000000005</v>
+        <v>3940.0800000000004</v>
       </c>
       <c r="AW11" s="30">
         <f t="shared" si="1"/>
-        <v>3921.1900000000005</v>
+        <v>3940.0800000000004</v>
       </c>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.25">
@@ -19329,49 +19332,25 @@
       <c r="AI15" s="7">
         <v>0</v>
       </c>
-      <c r="AJ15" s="7">
-        <v>250</v>
-      </c>
-      <c r="AK15" s="7">
-        <v>250</v>
-      </c>
-      <c r="AL15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AS15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AT15" s="7">
-        <v>0</v>
-      </c>
-      <c r="AU15" s="7">
-        <v>0</v>
-      </c>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
+      <c r="AM15" s="7"/>
+      <c r="AN15" s="7"/>
+      <c r="AO15" s="7"/>
+      <c r="AP15" s="7"/>
+      <c r="AQ15" s="7"/>
+      <c r="AR15" s="7"/>
+      <c r="AS15" s="7"/>
+      <c r="AT15" s="7"/>
+      <c r="AU15" s="7"/>
       <c r="AV15" s="7">
         <f t="shared" si="0"/>
-        <v>11550</v>
+        <v>11300</v>
       </c>
       <c r="AW15" s="28">
         <f t="shared" si="1"/>
-        <v>11550</v>
+        <v>11300</v>
       </c>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.25">
@@ -19480,49 +19459,25 @@
       <c r="AI16" s="9">
         <v>0</v>
       </c>
-      <c r="AJ16" s="8">
-        <v>250</v>
-      </c>
-      <c r="AK16" s="9">
-        <v>250</v>
-      </c>
-      <c r="AL16" s="8">
-        <v>0</v>
-      </c>
-      <c r="AM16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AN16" s="8">
-        <v>0</v>
-      </c>
-      <c r="AO16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AP16" s="8">
-        <v>0</v>
-      </c>
-      <c r="AQ16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AR16" s="8">
-        <v>0</v>
-      </c>
-      <c r="AS16" s="9">
-        <v>0</v>
-      </c>
-      <c r="AT16" s="8">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="9">
-        <v>0</v>
-      </c>
+      <c r="AJ16" s="8"/>
+      <c r="AK16" s="9"/>
+      <c r="AL16" s="8"/>
+      <c r="AM16" s="9"/>
+      <c r="AN16" s="8"/>
+      <c r="AO16" s="9"/>
+      <c r="AP16" s="8"/>
+      <c r="AQ16" s="9"/>
+      <c r="AR16" s="8"/>
+      <c r="AS16" s="9"/>
+      <c r="AT16" s="8"/>
+      <c r="AU16" s="9"/>
       <c r="AV16" s="8">
         <f t="shared" si="0"/>
-        <v>10850</v>
+        <v>10600</v>
       </c>
       <c r="AW16" s="30">
         <f t="shared" si="1"/>
-        <v>10850</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
@@ -19739,25 +19694,25 @@
         <v>-157937.47</v>
       </c>
       <c r="AJ18" s="10">
-        <v>-48056.32</v>
+        <v>-92992.5</v>
       </c>
       <c r="AK18" s="10">
-        <v>-10128.23</v>
+        <v>-92992.5</v>
       </c>
       <c r="AL18" s="10">
-        <v>-28049.02</v>
+        <v>-31250.98</v>
       </c>
       <c r="AM18" s="10">
         <v>0</v>
       </c>
       <c r="AN18" s="10">
-        <v>-26876.04</v>
+        <v>-27392.75</v>
       </c>
       <c r="AO18" s="10">
         <v>0</v>
       </c>
       <c r="AP18" s="10">
-        <v>-26870.97</v>
+        <v>-27159.79</v>
       </c>
       <c r="AQ18" s="10">
         <v>0</v>
@@ -19776,11 +19731,11 @@
       </c>
       <c r="AV18" s="10">
         <f t="shared" si="0"/>
-        <v>-1249435.3600000001</v>
+        <v>-1298379.03</v>
       </c>
       <c r="AW18" s="33">
         <f t="shared" si="1"/>
-        <v>-1076790.19</v>
+        <v>-1159654.46</v>
       </c>
     </row>
     <row r="19" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -19890,10 +19845,10 @@
         <v>-22798.69</v>
       </c>
       <c r="AJ19" s="7">
-        <v>-5000</v>
+        <v>-24120.53</v>
       </c>
       <c r="AK19" s="7">
-        <v>0</v>
+        <v>-24120.53</v>
       </c>
       <c r="AL19" s="7">
         <v>-5000</v>
@@ -19927,11 +19882,11 @@
       </c>
       <c r="AV19" s="7">
         <f t="shared" si="0"/>
-        <v>-144522.98000000001</v>
+        <v>-163643.51</v>
       </c>
       <c r="AW19" s="28">
         <f t="shared" si="1"/>
-        <v>-114540.77000000002</v>
+        <v>-138661.30000000002</v>
       </c>
     </row>
     <row r="20" spans="1:49" x14ac:dyDescent="0.25">
@@ -20041,10 +19996,10 @@
         <v>-22798.69</v>
       </c>
       <c r="AJ20" s="8">
-        <v>-5000</v>
+        <v>-24120.53</v>
       </c>
       <c r="AK20" s="9">
-        <v>0</v>
+        <v>-24120.53</v>
       </c>
       <c r="AL20" s="8">
         <v>-5000</v>
@@ -20078,11 +20033,11 @@
       </c>
       <c r="AV20" s="8">
         <f t="shared" si="0"/>
-        <v>-144522.98000000001</v>
+        <v>-163643.51</v>
       </c>
       <c r="AW20" s="30">
         <f t="shared" si="1"/>
-        <v>-114540.77000000002</v>
+        <v>-138661.30000000002</v>
       </c>
     </row>
     <row r="21" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20192,10 +20147,10 @@
         <v>-3364.15</v>
       </c>
       <c r="AJ21" s="7">
-        <v>-124.15</v>
+        <v>-3714.15</v>
       </c>
       <c r="AK21" s="7">
-        <v>0</v>
+        <v>-3714.15</v>
       </c>
       <c r="AL21" s="7">
         <v>-124.15</v>
@@ -20229,11 +20184,11 @@
       </c>
       <c r="AV21" s="7">
         <f t="shared" si="0"/>
-        <v>-51053.61</v>
+        <v>-54643.61</v>
       </c>
       <c r="AW21" s="28">
         <f t="shared" si="1"/>
-        <v>-50432.859999999993</v>
+        <v>-54147.009999999995</v>
       </c>
     </row>
     <row r="22" spans="1:49" x14ac:dyDescent="0.25">
@@ -20343,10 +20298,10 @@
         <v>-3364.15</v>
       </c>
       <c r="AJ22" s="8">
-        <v>-124.15</v>
+        <v>-3714.15</v>
       </c>
       <c r="AK22" s="9">
-        <v>0</v>
+        <v>-3714.15</v>
       </c>
       <c r="AL22" s="8">
         <v>-124.15</v>
@@ -20380,11 +20335,11 @@
       </c>
       <c r="AV22" s="8">
         <f t="shared" si="0"/>
-        <v>-26501.820000000018</v>
+        <v>-30091.820000000018</v>
       </c>
       <c r="AW22" s="30">
         <f t="shared" si="1"/>
-        <v>-25881.070000000011</v>
+        <v>-29595.220000000012</v>
       </c>
     </row>
     <row r="23" spans="1:49" x14ac:dyDescent="0.25">
@@ -20645,25 +20600,25 @@
         <v>-103788.84</v>
       </c>
       <c r="AJ24" s="7">
-        <v>-25848.19</v>
+        <v>-26337.19</v>
       </c>
       <c r="AK24" s="7">
-        <v>-5000</v>
+        <v>-26337.19</v>
       </c>
       <c r="AL24" s="7">
-        <v>-5828.89</v>
+        <v>-6755.02</v>
       </c>
       <c r="AM24" s="7">
         <v>0</v>
       </c>
       <c r="AN24" s="7">
-        <v>-5828.91</v>
+        <v>-6117.73</v>
       </c>
       <c r="AO24" s="7">
         <v>0</v>
       </c>
       <c r="AP24" s="7">
-        <v>-5828.91</v>
+        <v>-6117.73</v>
       </c>
       <c r="AQ24" s="7">
         <v>0</v>
@@ -20682,11 +20637,11 @@
       </c>
       <c r="AV24" s="7">
         <f t="shared" si="0"/>
-        <v>-514174.81</v>
+        <v>-516167.58</v>
       </c>
       <c r="AW24" s="28">
         <f t="shared" si="1"/>
-        <v>-464839.91000000003</v>
+        <v>-486177.10000000003</v>
       </c>
     </row>
     <row r="25" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20796,13 +20751,13 @@
         <v>-102545.68</v>
       </c>
       <c r="AJ25" s="11">
-        <v>-22261.77</v>
+        <v>-24261.77</v>
       </c>
       <c r="AK25" s="12">
-        <v>-5000</v>
+        <v>-24261.77</v>
       </c>
       <c r="AL25" s="11">
-        <v>-2500</v>
+        <v>-2553.9</v>
       </c>
       <c r="AM25" s="12">
         <v>0</v>
@@ -20833,11 +20788,11 @@
       </c>
       <c r="AV25" s="11">
         <f t="shared" si="0"/>
-        <v>-443311.74</v>
+        <v>-445365.64</v>
       </c>
       <c r="AW25" s="35">
         <f t="shared" si="1"/>
-        <v>-413549.97</v>
+        <v>-432811.74</v>
       </c>
     </row>
     <row r="26" spans="1:49" x14ac:dyDescent="0.25">
@@ -20950,7 +20905,7 @@
         <v>-2500</v>
       </c>
       <c r="AK26" s="9">
-        <v>0</v>
+        <v>-2500</v>
       </c>
       <c r="AL26" s="8">
         <v>-2500</v>
@@ -20988,7 +20943,7 @@
       </c>
       <c r="AW26" s="30">
         <f t="shared" si="1"/>
-        <v>-37500</v>
+        <v>-40000</v>
       </c>
     </row>
     <row r="27" spans="1:49" x14ac:dyDescent="0.25">
@@ -21098,13 +21053,13 @@
         <v>-100045.68</v>
       </c>
       <c r="AJ27" s="8">
-        <v>-19761.77</v>
+        <v>-21761.77</v>
       </c>
       <c r="AK27" s="9">
-        <v>-5000</v>
+        <v>-21761.77</v>
       </c>
       <c r="AL27" s="8">
-        <v>0</v>
+        <v>-53.9</v>
       </c>
       <c r="AM27" s="9">
         <v>0</v>
@@ -21135,11 +21090,11 @@
       </c>
       <c r="AV27" s="8">
         <f t="shared" si="0"/>
-        <v>-388777.41000000003</v>
+        <v>-390831.31000000006</v>
       </c>
       <c r="AW27" s="30">
         <f t="shared" si="1"/>
-        <v>-374015.64</v>
+        <v>-390777.41000000003</v>
       </c>
     </row>
     <row r="28" spans="1:49" x14ac:dyDescent="0.25">
@@ -21352,25 +21307,25 @@
         <v>-1243.1600000000001</v>
       </c>
       <c r="AJ29" s="11">
-        <v>-3586.42</v>
+        <v>-2075.42</v>
       </c>
       <c r="AK29" s="12">
-        <v>0</v>
+        <v>-2075.42</v>
       </c>
       <c r="AL29" s="11">
-        <v>-3328.89</v>
+        <v>-4201.12</v>
       </c>
       <c r="AM29" s="12">
         <v>0</v>
       </c>
       <c r="AN29" s="11">
-        <v>-3328.91</v>
+        <v>-3617.73</v>
       </c>
       <c r="AO29" s="12">
         <v>0</v>
       </c>
       <c r="AP29" s="11">
-        <v>-3328.91</v>
+        <v>-3617.73</v>
       </c>
       <c r="AQ29" s="12">
         <v>0</v>
@@ -21389,11 +21344,11 @@
       </c>
       <c r="AV29" s="11">
         <f t="shared" si="0"/>
-        <v>-70863.070000000007</v>
+        <v>-70801.94</v>
       </c>
       <c r="AW29" s="35">
         <f t="shared" si="1"/>
-        <v>-51289.94</v>
+        <v>-53365.36</v>
       </c>
     </row>
     <row r="30" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -21455,7 +21410,7 @@
       <c r="AH30" s="11"/>
       <c r="AI30" s="12"/>
       <c r="AJ30" s="16">
-        <v>-3000</v>
+        <v>0</v>
       </c>
       <c r="AK30" s="17">
         <v>0</v>
@@ -21492,7 +21447,7 @@
       </c>
       <c r="AV30" s="16">
         <f t="shared" si="0"/>
-        <v>-18000</v>
+        <v>-15000</v>
       </c>
       <c r="AW30" s="35">
         <f t="shared" si="1"/>
@@ -21955,25 +21910,25 @@
         <v>-1243.1600000000001</v>
       </c>
       <c r="AJ34" s="8">
-        <v>-586.41999999999996</v>
+        <v>-2075.42</v>
       </c>
       <c r="AK34" s="9">
-        <v>0</v>
+        <v>-2075.42</v>
       </c>
       <c r="AL34" s="8">
-        <v>-328.91</v>
+        <v>-1201.1199999999999</v>
       </c>
       <c r="AM34" s="9">
         <v>0</v>
       </c>
       <c r="AN34" s="8">
-        <v>-328.91</v>
+        <v>-617.73</v>
       </c>
       <c r="AO34" s="9">
         <v>0</v>
       </c>
       <c r="AP34" s="8">
-        <v>-328.91</v>
+        <v>-617.73</v>
       </c>
       <c r="AQ34" s="9">
         <v>0</v>
@@ -21992,11 +21947,11 @@
       </c>
       <c r="AV34" s="8">
         <f t="shared" si="0"/>
-        <v>-43211.470000000008</v>
+        <v>-46150.320000000007</v>
       </c>
       <c r="AW34" s="30">
         <f t="shared" si="1"/>
-        <v>-41638.32</v>
+        <v>-43713.74</v>
       </c>
     </row>
     <row r="35" spans="1:49" x14ac:dyDescent="0.25">
@@ -22229,19 +22184,19 @@
         <v>-9713.24</v>
       </c>
       <c r="AJ36" s="7">
-        <v>-7154.53</v>
+        <v>-27891.18</v>
       </c>
       <c r="AK36" s="7">
-        <v>-5007.05</v>
+        <v>-27891.18</v>
       </c>
       <c r="AL36" s="7">
-        <v>-11552.69</v>
+        <v>-13404.28</v>
       </c>
       <c r="AM36" s="7">
         <v>0</v>
       </c>
       <c r="AN36" s="7">
-        <v>-10922.98</v>
+        <v>-11150.87</v>
       </c>
       <c r="AO36" s="7">
         <v>0</v>
@@ -22266,11 +22221,11 @@
       </c>
       <c r="AV36" s="7">
         <f t="shared" si="0"/>
-        <v>-293388.69999999995</v>
+        <v>-316204.82999999996</v>
       </c>
       <c r="AW36" s="28">
         <f t="shared" si="1"/>
-        <v>-236032.95</v>
+        <v>-258917.08000000002</v>
       </c>
     </row>
     <row r="37" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -22380,10 +22335,10 @@
         <v>-4359.6000000000004</v>
       </c>
       <c r="AJ37" s="11">
-        <v>-4367.6099999999997</v>
+        <v>-4367.6499999999996</v>
       </c>
       <c r="AK37" s="12">
-        <v>-3535.86</v>
+        <v>-4367.6499999999996</v>
       </c>
       <c r="AL37" s="11">
         <v>-4281.75</v>
@@ -22417,11 +22372,11 @@
       </c>
       <c r="AV37" s="11">
         <f t="shared" si="0"/>
-        <v>-92647.77</v>
+        <v>-92647.81</v>
       </c>
       <c r="AW37" s="35">
         <f t="shared" si="1"/>
-        <v>-70394.929999999993</v>
+        <v>-71226.719999999987</v>
       </c>
     </row>
     <row r="38" spans="1:49" x14ac:dyDescent="0.25">
@@ -22534,7 +22489,7 @@
         <v>-1100</v>
       </c>
       <c r="AK38" s="9">
-        <v>-400</v>
+        <v>-1100</v>
       </c>
       <c r="AL38" s="8">
         <v>-1100</v>
@@ -22572,7 +22527,7 @@
       </c>
       <c r="AW38" s="30">
         <f t="shared" si="1"/>
-        <v>-12800</v>
+        <v>-13500</v>
       </c>
     </row>
     <row r="39" spans="1:49" x14ac:dyDescent="0.25">
@@ -23286,10 +23241,10 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="8">
-        <v>-131.75</v>
+        <v>-131.79</v>
       </c>
       <c r="AK43" s="9">
-        <v>0</v>
+        <v>-131.79</v>
       </c>
       <c r="AL43" s="8">
         <v>-131.75</v>
@@ -23323,11 +23278,11 @@
       </c>
       <c r="AV43" s="8">
         <f t="shared" si="0"/>
-        <v>-2869.27</v>
+        <v>-2869.31</v>
       </c>
       <c r="AW43" s="30">
         <f t="shared" si="1"/>
-        <v>-2084.2199999999998</v>
+        <v>-2216.0099999999998</v>
       </c>
     </row>
     <row r="44" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -23437,10 +23392,10 @@
         <v>-2948.5</v>
       </c>
       <c r="AJ44" s="11">
-        <v>-2329.89</v>
+        <v>-22348.2</v>
       </c>
       <c r="AK44" s="12">
-        <v>-1442.69</v>
+        <v>-22348.2</v>
       </c>
       <c r="AL44" s="11">
         <v>-7265.87</v>
@@ -23474,11 +23429,11 @@
       </c>
       <c r="AV44" s="11">
         <f t="shared" si="0"/>
-        <v>-156382.9</v>
+        <v>-176401.21000000002</v>
       </c>
       <c r="AW44" s="35">
         <f t="shared" si="1"/>
-        <v>-121718.66</v>
+        <v>-142624.17000000001</v>
       </c>
     </row>
     <row r="45" spans="1:49" x14ac:dyDescent="0.25">
@@ -23591,7 +23546,7 @@
         <v>-727.2</v>
       </c>
       <c r="AK45" s="9">
-        <v>0</v>
+        <v>-727.2</v>
       </c>
       <c r="AL45" s="8">
         <v>-663.18</v>
@@ -23629,7 +23584,7 @@
       </c>
       <c r="AW45" s="30">
         <f t="shared" si="1"/>
-        <v>-4270.8999999999996</v>
+        <v>-4998.0999999999995</v>
       </c>
     </row>
     <row r="46" spans="1:49" x14ac:dyDescent="0.25">
@@ -23739,10 +23694,10 @@
         <v>-1127.5</v>
       </c>
       <c r="AJ46" s="8">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="AK46" s="9">
-        <v>0</v>
+        <v>-20000</v>
       </c>
       <c r="AL46" s="8">
         <v>-5000</v>
@@ -23776,11 +23731,11 @@
       </c>
       <c r="AV46" s="8">
         <f t="shared" si="0"/>
-        <v>-117650.51999999999</v>
+        <v>-137650.51999999999</v>
       </c>
       <c r="AW46" s="30">
         <f t="shared" si="1"/>
-        <v>-92650.51999999999</v>
+        <v>-112650.51999999999</v>
       </c>
     </row>
     <row r="47" spans="1:49" x14ac:dyDescent="0.25">
@@ -23890,10 +23845,10 @@
         <v>-178.31</v>
       </c>
       <c r="AJ47" s="8">
-        <v>-160</v>
+        <v>-178.31</v>
       </c>
       <c r="AK47" s="9">
-        <v>0</v>
+        <v>-178.31</v>
       </c>
       <c r="AL47" s="8">
         <v>-160</v>
@@ -23927,11 +23882,11 @@
       </c>
       <c r="AV47" s="8">
         <f t="shared" si="0"/>
-        <v>-3521.35</v>
+        <v>-3539.66</v>
       </c>
       <c r="AW47" s="30">
         <f t="shared" si="1"/>
-        <v>-2561.35</v>
+        <v>-2739.66</v>
       </c>
     </row>
     <row r="48" spans="1:49" x14ac:dyDescent="0.25">
@@ -24295,19 +24250,19 @@
         <v>-2405.14</v>
       </c>
       <c r="AJ50" s="11">
-        <v>-457.03</v>
+        <v>-1175.33</v>
       </c>
       <c r="AK50" s="12">
-        <v>-28.5</v>
+        <v>-1175.33</v>
       </c>
       <c r="AL50" s="11">
-        <v>-5.07</v>
+        <v>-1856.66</v>
       </c>
       <c r="AM50" s="12">
         <v>0</v>
       </c>
       <c r="AN50" s="11">
-        <v>-5.07</v>
+        <v>-232.96</v>
       </c>
       <c r="AO50" s="12">
         <v>0</v>
@@ -24332,11 +24287,11 @@
       </c>
       <c r="AV50" s="11">
         <f t="shared" si="0"/>
-        <v>-44358.029999999992</v>
+        <v>-47155.81</v>
       </c>
       <c r="AW50" s="35">
         <f t="shared" si="1"/>
-        <v>-43919.359999999993</v>
+        <v>-45066.189999999995</v>
       </c>
     </row>
     <row r="51" spans="1:49" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -24548,21 +24503,45 @@
       </c>
       <c r="AH52" s="8"/>
       <c r="AI52" s="9"/>
-      <c r="AJ52" s="8"/>
-      <c r="AK52" s="9"/>
-      <c r="AL52" s="8"/>
-      <c r="AM52" s="9"/>
-      <c r="AN52" s="8"/>
-      <c r="AO52" s="9"/>
-      <c r="AP52" s="8"/>
-      <c r="AQ52" s="9"/>
-      <c r="AR52" s="8"/>
-      <c r="AS52" s="9"/>
-      <c r="AT52" s="8"/>
-      <c r="AU52" s="9"/>
+      <c r="AJ52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AL52" s="8">
+        <v>-29.98</v>
+      </c>
+      <c r="AM52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="9">
+        <v>0</v>
+      </c>
       <c r="AV52" s="8">
         <f t="shared" si="0"/>
-        <v>-507.07000000000005</v>
+        <v>-537.05000000000007</v>
       </c>
       <c r="AW52" s="30">
         <f t="shared" si="1"/>
@@ -24671,25 +24650,49 @@
       </c>
       <c r="AH53" s="8"/>
       <c r="AI53" s="9"/>
-      <c r="AJ53" s="8"/>
-      <c r="AK53" s="9"/>
-      <c r="AL53" s="8"/>
-      <c r="AM53" s="9"/>
-      <c r="AN53" s="8"/>
-      <c r="AO53" s="9"/>
-      <c r="AP53" s="8"/>
-      <c r="AQ53" s="9"/>
-      <c r="AR53" s="8"/>
-      <c r="AS53" s="9"/>
-      <c r="AT53" s="8"/>
-      <c r="AU53" s="9"/>
+      <c r="AJ53" s="8">
+        <v>-90.3</v>
+      </c>
+      <c r="AK53" s="9">
+        <v>-90.3</v>
+      </c>
+      <c r="AL53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU53" s="9">
+        <v>0</v>
+      </c>
       <c r="AV53" s="8">
         <f t="shared" si="0"/>
-        <v>-422.4</v>
+        <v>-512.69999999999993</v>
       </c>
       <c r="AW53" s="30">
         <f t="shared" si="1"/>
-        <v>-422.4</v>
+        <v>-512.69999999999993</v>
       </c>
     </row>
     <row r="54" spans="1:49" x14ac:dyDescent="0.25">
@@ -25148,19 +25151,19 @@
         <v>-201.19</v>
       </c>
       <c r="AJ57" s="8">
-        <v>0</v>
+        <v>-628</v>
       </c>
       <c r="AK57" s="9">
-        <v>0</v>
+        <v>-628</v>
       </c>
       <c r="AL57" s="8">
-        <v>0</v>
+        <v>-764.88</v>
       </c>
       <c r="AM57" s="9">
         <v>0</v>
       </c>
       <c r="AN57" s="8">
-        <v>0</v>
+        <v>-227.89</v>
       </c>
       <c r="AO57" s="9">
         <v>0</v>
@@ -25185,11 +25188,11 @@
       </c>
       <c r="AV57" s="8">
         <f t="shared" si="0"/>
-        <v>-16191.560000000001</v>
+        <v>-17812.330000000002</v>
       </c>
       <c r="AW57" s="30">
         <f t="shared" si="1"/>
-        <v>-16191.560000000001</v>
+        <v>-16819.560000000001</v>
       </c>
     </row>
     <row r="58" spans="1:49" x14ac:dyDescent="0.25">
@@ -25302,10 +25305,10 @@
         <v>-428.53</v>
       </c>
       <c r="AK58" s="9">
-        <v>0</v>
+        <v>-428.53</v>
       </c>
       <c r="AL58" s="8">
-        <v>-5.07</v>
+        <v>-1061.8</v>
       </c>
       <c r="AM58" s="9">
         <v>0</v>
@@ -25336,11 +25339,11 @@
       </c>
       <c r="AV58" s="8">
         <f t="shared" si="0"/>
-        <v>-9607.36</v>
+        <v>-10664.09</v>
       </c>
       <c r="AW58" s="30">
         <f t="shared" si="1"/>
-        <v>-9168.69</v>
+        <v>-9597.2200000000012</v>
       </c>
     </row>
     <row r="59" spans="1:49" x14ac:dyDescent="0.25">
@@ -26489,10 +26492,10 @@
         <v>-25.98</v>
       </c>
       <c r="AK67" s="7">
-        <v>0</v>
+        <v>-25.98</v>
       </c>
       <c r="AL67" s="7">
-        <v>0</v>
+        <v>-33.840000000000003</v>
       </c>
       <c r="AM67" s="7">
         <v>0</v>
@@ -26523,11 +26526,11 @@
       </c>
       <c r="AV67" s="7">
         <f t="shared" si="0"/>
-        <v>-2920.09</v>
+        <v>-2953.9300000000003</v>
       </c>
       <c r="AW67" s="28">
         <f t="shared" si="1"/>
-        <v>-2894.11</v>
+        <v>-2920.09</v>
       </c>
     </row>
     <row r="68" spans="1:49" x14ac:dyDescent="0.25">
@@ -26640,10 +26643,10 @@
         <v>-25.98</v>
       </c>
       <c r="AK68" s="9">
-        <v>0</v>
+        <v>-25.98</v>
       </c>
       <c r="AL68" s="8">
-        <v>0</v>
+        <v>-33.840000000000003</v>
       </c>
       <c r="AM68" s="9">
         <v>0</v>
@@ -26674,11 +26677,11 @@
       </c>
       <c r="AV68" s="8">
         <f t="shared" si="0"/>
-        <v>-430.7700000000001</v>
+        <v>-464.61000000000013</v>
       </c>
       <c r="AW68" s="30">
         <f t="shared" si="1"/>
-        <v>-404.79000000000008</v>
+        <v>-430.7700000000001</v>
       </c>
     </row>
     <row r="69" spans="1:49" x14ac:dyDescent="0.25">
@@ -27165,13 +27168,13 @@
         <v>-17151.73</v>
       </c>
       <c r="AJ72" s="7">
-        <v>-5000</v>
+        <v>-6000</v>
       </c>
       <c r="AK72" s="7">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="AL72" s="7">
-        <v>-5000</v>
+        <v>-5390.4</v>
       </c>
       <c r="AM72" s="7">
         <v>0</v>
@@ -27202,11 +27205,11 @@
       </c>
       <c r="AV72" s="7">
         <f t="shared" si="2"/>
-        <v>-92865.94</v>
+        <v>-94256.34</v>
       </c>
       <c r="AW72" s="28">
         <f t="shared" si="3"/>
-        <v>-62865.94</v>
+        <v>-68865.94</v>
       </c>
     </row>
     <row r="73" spans="1:49" s="14" customFormat="1" x14ac:dyDescent="0.25">
@@ -27387,25 +27390,49 @@
       </c>
       <c r="AH74" s="8"/>
       <c r="AI74" s="9"/>
-      <c r="AJ74" s="8"/>
-      <c r="AK74" s="9"/>
-      <c r="AL74" s="8"/>
-      <c r="AM74" s="9"/>
-      <c r="AN74" s="8"/>
-      <c r="AO74" s="9"/>
-      <c r="AP74" s="8"/>
-      <c r="AQ74" s="9"/>
-      <c r="AR74" s="8"/>
-      <c r="AS74" s="9"/>
-      <c r="AT74" s="8"/>
-      <c r="AU74" s="9"/>
+      <c r="AJ74" s="8">
+        <v>-1000</v>
+      </c>
+      <c r="AK74" s="9">
+        <v>-1000</v>
+      </c>
+      <c r="AL74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AM74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AN74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AO74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AQ74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AR74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AS74" s="9">
+        <v>0</v>
+      </c>
+      <c r="AT74" s="8">
+        <v>0</v>
+      </c>
+      <c r="AU74" s="9">
+        <v>0</v>
+      </c>
       <c r="AV74" s="8">
         <f t="shared" si="2"/>
-        <v>-3897.45</v>
+        <v>-4897.45</v>
       </c>
       <c r="AW74" s="30">
         <f t="shared" si="3"/>
-        <v>-3897.45</v>
+        <v>-4897.45</v>
       </c>
     </row>
     <row r="75" spans="1:49" x14ac:dyDescent="0.25">
@@ -27454,7 +27481,7 @@
         <v>-5000</v>
       </c>
       <c r="AK75" s="9">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="AL75" s="8">
         <v>-5000</v>
@@ -27722,7 +27749,7 @@
         <v>-4842.53</v>
       </c>
       <c r="AK77" s="7">
-        <v>-60.24</v>
+        <v>-4842.53</v>
       </c>
       <c r="AL77" s="7">
         <v>-543.29</v>
@@ -27760,7 +27787,7 @@
       </c>
       <c r="AW77" s="28">
         <f t="shared" si="3"/>
-        <v>-143266.52000000002</v>
+        <v>-148048.81000000003</v>
       </c>
     </row>
     <row r="78" spans="1:49" x14ac:dyDescent="0.25">
@@ -27873,7 +27900,7 @@
         <v>-4842.53</v>
       </c>
       <c r="AK78" s="9">
-        <v>-60.24</v>
+        <v>-4842.53</v>
       </c>
       <c r="AL78" s="8">
         <v>-543.29</v>
@@ -27911,7 +27938,7 @@
       </c>
       <c r="AW78" s="30">
         <f t="shared" si="3"/>
-        <v>-143266.52000000002</v>
+        <v>-148048.81000000003</v>
       </c>
     </row>
     <row r="79" spans="1:49" s="15" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -28021,37 +28048,37 @@
         <v>36274.720000000001</v>
       </c>
       <c r="AJ79" s="41">
-        <v>118611.32</v>
+        <v>89602.81</v>
       </c>
       <c r="AK79" s="5">
-        <v>36793.97</v>
+        <v>65098.51</v>
       </c>
       <c r="AL79" s="41">
-        <v>26047</v>
+        <v>44265.04</v>
       </c>
       <c r="AM79" s="5">
         <v>0</v>
       </c>
       <c r="AN79" s="41">
-        <v>-11673.66</v>
+        <v>-8509.01</v>
       </c>
       <c r="AO79" s="5">
         <v>0</v>
       </c>
       <c r="AP79" s="41">
-        <v>-18604.080000000002</v>
+        <v>-16303.44</v>
       </c>
       <c r="AQ79" s="5">
         <v>0</v>
       </c>
       <c r="AR79" s="41">
-        <v>-21873.4</v>
+        <v>-19283.939999999999</v>
       </c>
       <c r="AS79" s="5">
         <v>0</v>
       </c>
       <c r="AT79" s="41">
-        <v>-24709</v>
+        <v>-22799.54</v>
       </c>
       <c r="AU79" s="5">
         <v>0</v>
@@ -28166,46 +28193,58 @@
         <v>375744.29</v>
       </c>
       <c r="AJ80" s="42">
-        <v>646519.23</v>
+        <v>617510.72</v>
       </c>
       <c r="AK80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AL80" s="42">
-        <v>672566.23</v>
+        <v>661775.76</v>
       </c>
       <c r="AM80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AN80" s="42">
-        <v>660892.56999999995</v>
+        <v>653266.75</v>
       </c>
       <c r="AO80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AP80" s="42">
-        <v>642288.49</v>
+        <v>636963.31000000006</v>
       </c>
       <c r="AQ80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AR80" s="42">
-        <v>620415.09</v>
+        <v>617679.37</v>
       </c>
       <c r="AS80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AT80" s="42">
-        <v>595706.09</v>
+        <v>594879.82999999996</v>
       </c>
       <c r="AU80" s="39">
-        <v>412538.26</v>
+        <v>440842.8</v>
       </c>
       <c r="AV80" s="42"/>
       <c r="AW80" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="L1:M1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="R1:S1"/>
+    <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AD1:AE1"/>
+    <mergeCell ref="AF1:AG1"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="J1:K1"/>
     <mergeCell ref="AV1:AW1"/>
     <mergeCell ref="T1:U1"/>
     <mergeCell ref="V1:W1"/>
@@ -28218,18 +28257,6 @@
     <mergeCell ref="AP1:AQ1"/>
     <mergeCell ref="AR1:AS1"/>
     <mergeCell ref="AT1:AU1"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:I1"/>
-    <mergeCell ref="J1:K1"/>
-    <mergeCell ref="L1:M1"/>
-    <mergeCell ref="N1:O1"/>
-    <mergeCell ref="P1:Q1"/>
-    <mergeCell ref="R1:S1"/>
-    <mergeCell ref="AH1:AI1"/>
-    <mergeCell ref="AD1:AE1"/>
-    <mergeCell ref="AF1:AG1"/>
   </mergeCells>
   <conditionalFormatting sqref="A4:AW4">
     <cfRule type="cellIs" dxfId="5" priority="5" operator="greaterThan">
@@ -28287,10 +28314,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ADA578-B5E1-45EA-8993-7C8958BB27A1}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="43.7109375" customWidth="1"/>
+    <col min="1" max="1" width="49.42578125" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" customWidth="1"/>
   </cols>
@@ -28436,6 +28463,17 @@
       </c>
       <c r="C13" s="2">
         <v>921.61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" t="s">
+        <v>159</v>
+      </c>
+      <c r="C14" s="2">
+        <v>875.75</v>
       </c>
     </row>
   </sheetData>
